--- a/docagent_clean_mvp/sample_data/raw_excels/ISO27001_SetB.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/ISO27001_SetB.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>An information security policy is approved by senior management and reviewed at least annually.</t>
+          <t>Standard Organizational Controls policy mandates that an information security policy is approved by senior management and reviewed at least annually. [ISO27001-005]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Compliant - policy v3.2 approved by CISO</t>
+          <t>Compliant - evidence on file</t>
         </is>
       </c>
     </row>
